--- a/results/job_matches_2026-09-21.xlsx
+++ b/results/job_matches_2026-09-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,1715 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pj Dick-Trumbull-Lindy Group</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AWS Cloud Administrator</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wexford, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e707c3d7c8fd8897</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ignite Insurance Systems</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FourLeaf Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bethpage, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Junior Backend Software Developer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quantic</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Exton, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ecdb24fded8712c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ShipStation Global</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=028e43335938f143</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ShipStation Global</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5966248554dc0bb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mid-Level Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Antra, Inc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Engineer IV (6329)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>itD Tech</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4007bc63b344853</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer I, Burger King</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Burger King</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77aeab60d6ba5f5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Boats Group</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Athena, S3, SQS, ECS, IAM, RDS, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917ce891fbb59294</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vforce Infotech</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d93b899dbf5eaf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - GCP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d4fb8c5ae21e05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>LTM Limited</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Raleigh, NC, US USA</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D15" t="n">
         <v>12.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, MySQL, Dimensional Modeling</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e87eafcc6ca3f52f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Veradigm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deepwatch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer II</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ActioNet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ActioNet</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Suitland, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83c02567e875c724</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>West Lafayette, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52a9d0a4fe41bcb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9908194ee52c240</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d06caa1f573b5e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80229a4fad29b8e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e702bf50ec0d208</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA Material Master Solution Architect / Senior MM Architect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sdna global</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d63f66f6aa5ca957</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Simpson Strong-Tie</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Contact center Architect - Amazon Connect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RPA INFOTECH INDIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8011e2e01cd1c12</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Aegis Mobile</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Power BI, Tableau, MLOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Multi- Cloud Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cywarden, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, IAM, Azure, GCP, Scala, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90096161c263b413</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Technical Implementations Specialist (US)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Activated Insights</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d911c664f1ca9e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7519f106646cfafb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Golang, AWS)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9769cef0a6e3ea3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ness Digital Engineering</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, Power BI, Terraform</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Superior Automotive Group</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>IAM, BigQuery, Dataflow, Vertex AI, Dimensional Modeling, dbt, Power BI, Tableau, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=078b97b2887a3962</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (SAP BTP/CAP)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (SAP BTP/CAP)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88d251cc0fd62f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Database Administrator I</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Transcor Data Services</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83390bad559122e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openjobs</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=355f6f1ee2c253ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, Tableau</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d42fb889c5ed759</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Smart Apply Test Company</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Leesburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8e3fe265983e59b</t>
         </is>
       </c>
     </row>
